--- a/backend/data/financials_by_company/017480.KQ.xlsx
+++ b/backend/data/financials_by_company/017480.KQ.xlsx
@@ -662,580 +662,580 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>42704379.177489</v>
+        <v>-60123734.062886</v>
       </c>
       <c r="C2" t="n">
-        <v>0.200835</v>
+        <v>0.247524</v>
       </c>
       <c r="D2" t="n">
-        <v>4913742100</v>
+        <v>35973830020</v>
       </c>
       <c r="E2" t="n">
-        <v>212634000</v>
+        <v>-242901000</v>
       </c>
       <c r="F2" t="n">
-        <v>212634000</v>
+        <v>-242901000</v>
       </c>
       <c r="G2" t="n">
-        <v>5508284890</v>
+        <v>25395535400</v>
       </c>
       <c r="H2" t="n">
-        <v>1566517000</v>
+        <v>1979120000</v>
       </c>
       <c r="I2" t="n">
-        <v>211988698810</v>
+        <v>280493927190</v>
       </c>
       <c r="J2" t="n">
-        <v>5126376100</v>
+        <v>35730929020</v>
       </c>
       <c r="K2" t="n">
-        <v>3559859100</v>
+        <v>33751809020</v>
       </c>
       <c r="L2" t="n">
-        <v>2540333380</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
+        <v>350771090</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2530000</v>
+      </c>
       <c r="N2" t="n">
-        <v>2540333000</v>
+        <v>353301000</v>
       </c>
       <c r="O2" t="n">
-        <v>5338355269.177489</v>
+        <v>25578312665.93711</v>
       </c>
       <c r="P2" t="n">
-        <v>5508284890</v>
+        <v>25395535400</v>
       </c>
       <c r="Q2" t="n">
-        <v>220101647810</v>
+        <v>288998100190</v>
       </c>
       <c r="R2" t="n">
-        <v>3559859450</v>
+        <v>33148768680</v>
       </c>
       <c r="S2" t="n">
-        <v>15429369</v>
+        <v>15447406</v>
       </c>
       <c r="T2" t="n">
-        <v>15429369</v>
+        <v>15447406</v>
       </c>
       <c r="U2" t="n">
-        <v>357</v>
+        <v>1644</v>
       </c>
       <c r="V2" t="n">
-        <v>357</v>
+        <v>1644</v>
       </c>
       <c r="W2" t="n">
-        <v>5508284890</v>
+        <v>25395535400</v>
       </c>
       <c r="X2" t="n">
-        <v>5508284890</v>
+        <v>25395535400</v>
       </c>
       <c r="Y2" t="n">
-        <v>5508284890</v>
+        <v>25395535400</v>
       </c>
       <c r="Z2" t="n">
-        <v>5508284890</v>
+        <v>25395535400</v>
       </c>
       <c r="AA2" t="n">
-        <v>1384266530</v>
+        <v>8353743610</v>
       </c>
       <c r="AB2" t="n">
-        <v>6892551420</v>
+        <v>33749279020</v>
       </c>
       <c r="AC2" t="n">
-        <v>593440000</v>
+        <v>220152000</v>
       </c>
       <c r="AD2" t="n">
-        <v>167374000</v>
+        <v>-253416000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-167374000</v>
+        <v>253416000</v>
       </c>
       <c r="AF2" t="n">
-        <v>2540333380</v>
+        <v>350771090</v>
       </c>
       <c r="AG2" t="n">
-        <v>-380</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>-90</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2530000</v>
+      </c>
       <c r="AI2" t="n">
-        <v>2540333000</v>
+        <v>353301000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3559859100</v>
+        <v>33148768340</v>
       </c>
       <c r="AK2" t="n">
-        <v>8112949000</v>
+        <v>8504173000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-285435000</v>
+        <v>-311080000</v>
       </c>
       <c r="AM2" t="n">
-        <v>144709000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>6200000</v>
-      </c>
+        <v>207062000</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>138509000</v>
+        <v>207062000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3331577000</v>
+        <v>3076769000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2815619000</v>
+        <v>2420813000</v>
       </c>
       <c r="AR2" t="n">
-        <v>515958000</v>
+        <v>655956000</v>
       </c>
       <c r="AS2" t="n">
-        <v>11672808100</v>
+        <v>41652941340</v>
       </c>
       <c r="AT2" t="n">
-        <v>211988698810</v>
+        <v>280493927190</v>
       </c>
       <c r="AU2" t="n">
-        <v>223661506910</v>
+        <v>322146868530</v>
       </c>
       <c r="AV2" t="n">
-        <v>223661506910</v>
+        <v>322146868530</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-21301230.364085</v>
+        <v>30651038.041018</v>
       </c>
       <c r="C3" t="n">
-        <v>0.200595</v>
+        <v>0.248781</v>
       </c>
       <c r="D3" t="n">
-        <v>14899848610</v>
+        <v>23114036910</v>
       </c>
       <c r="E3" t="n">
-        <v>-106190000</v>
+        <v>123205000</v>
       </c>
       <c r="F3" t="n">
-        <v>-106190000</v>
+        <v>123205000</v>
       </c>
       <c r="G3" t="n">
-        <v>10414244120</v>
+        <v>16010830220</v>
       </c>
       <c r="H3" t="n">
-        <v>1766057000</v>
+        <v>1922804000</v>
       </c>
       <c r="I3" t="n">
-        <v>244236258410</v>
+        <v>311627303510</v>
       </c>
       <c r="J3" t="n">
-        <v>14793658610</v>
+        <v>23237241910</v>
       </c>
       <c r="K3" t="n">
-        <v>13027601610</v>
+        <v>21314437910</v>
       </c>
       <c r="L3" t="n">
-        <v>2453959690</v>
+        <v>914796850</v>
       </c>
       <c r="M3" t="n">
-        <v>100000</v>
+        <v>1311000</v>
       </c>
       <c r="N3" t="n">
-        <v>2454061000</v>
+        <v>916109000</v>
       </c>
       <c r="O3" t="n">
-        <v>10499132889.63592</v>
+        <v>15918276258.04102</v>
       </c>
       <c r="P3" t="n">
-        <v>10414244120</v>
+        <v>16010830220</v>
       </c>
       <c r="Q3" t="n">
-        <v>252710058410</v>
+        <v>321440945510</v>
       </c>
       <c r="R3" t="n">
-        <v>9727719980</v>
+        <v>19125865550</v>
       </c>
       <c r="S3" t="n">
-        <v>15451401</v>
+        <v>15439566</v>
       </c>
       <c r="T3" t="n">
-        <v>15451401</v>
+        <v>15439566</v>
       </c>
       <c r="U3" t="n">
-        <v>674</v>
+        <v>1037</v>
       </c>
       <c r="V3" t="n">
-        <v>674</v>
+        <v>1037</v>
       </c>
       <c r="W3" t="n">
-        <v>10414244120</v>
+        <v>16010830220</v>
       </c>
       <c r="X3" t="n">
-        <v>10414244120</v>
+        <v>16010830220</v>
       </c>
       <c r="Y3" t="n">
-        <v>10414244120</v>
+        <v>16010830220</v>
       </c>
       <c r="Z3" t="n">
-        <v>10414244120</v>
+        <v>16010830220</v>
       </c>
       <c r="AA3" t="n">
-        <v>2613257490</v>
+        <v>5302296690</v>
       </c>
       <c r="AB3" t="n">
-        <v>13027501610</v>
+        <v>21313126910</v>
       </c>
       <c r="AC3" t="n">
-        <v>892141000</v>
+        <v>710780000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-3793000</v>
+        <v>123205000</v>
       </c>
       <c r="AE3" t="n">
-        <v>3793000</v>
+        <v>-123205000</v>
       </c>
       <c r="AF3" t="n">
-        <v>2453959690</v>
+        <v>914796850</v>
       </c>
       <c r="AG3" t="n">
-        <v>1310</v>
+        <v>1150</v>
       </c>
       <c r="AH3" t="n">
-        <v>100000</v>
+        <v>1311000</v>
       </c>
       <c r="AI3" t="n">
-        <v>2454061000</v>
+        <v>916109000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9727719600</v>
+        <v>19125865300</v>
       </c>
       <c r="AK3" t="n">
-        <v>8473800000</v>
+        <v>9813642000</v>
       </c>
       <c r="AL3" t="n">
-        <v>34714000</v>
+        <v>1069187000</v>
       </c>
       <c r="AM3" t="n">
-        <v>159390000</v>
+        <v>192935000</v>
       </c>
       <c r="AN3" t="n">
-        <v>6200000</v>
+        <v>517000</v>
       </c>
       <c r="AO3" t="n">
-        <v>153190000</v>
+        <v>192418000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3166873000</v>
+        <v>3278887000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2620333000</v>
+        <v>2691919000</v>
       </c>
       <c r="AR3" t="n">
-        <v>546540000</v>
+        <v>586968000</v>
       </c>
       <c r="AS3" t="n">
-        <v>18201519600</v>
+        <v>28939507300</v>
       </c>
       <c r="AT3" t="n">
-        <v>244236258410</v>
+        <v>311627303510</v>
       </c>
       <c r="AU3" t="n">
-        <v>262437778010</v>
+        <v>340566810810</v>
       </c>
       <c r="AV3" t="n">
-        <v>262437778010</v>
+        <v>340566810810</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>30651038.041018</v>
+        <v>-21301230.364085</v>
       </c>
       <c r="C4" t="n">
-        <v>0.248781</v>
+        <v>0.200595</v>
       </c>
       <c r="D4" t="n">
-        <v>23114036910</v>
+        <v>14899848610</v>
       </c>
       <c r="E4" t="n">
-        <v>123205000</v>
+        <v>-106190000</v>
       </c>
       <c r="F4" t="n">
-        <v>123205000</v>
+        <v>-106190000</v>
       </c>
       <c r="G4" t="n">
-        <v>16010830220</v>
+        <v>10414244120</v>
       </c>
       <c r="H4" t="n">
-        <v>1922804000</v>
+        <v>1766057000</v>
       </c>
       <c r="I4" t="n">
-        <v>311627303510</v>
+        <v>244236258410</v>
       </c>
       <c r="J4" t="n">
-        <v>23237241910</v>
+        <v>14793658610</v>
       </c>
       <c r="K4" t="n">
-        <v>21314437910</v>
+        <v>13027601610</v>
       </c>
       <c r="L4" t="n">
-        <v>914796850</v>
+        <v>2453959690</v>
       </c>
       <c r="M4" t="n">
-        <v>1311000</v>
+        <v>100000</v>
       </c>
       <c r="N4" t="n">
-        <v>916109000</v>
+        <v>2454061000</v>
       </c>
       <c r="O4" t="n">
-        <v>15918276258.04102</v>
+        <v>10499132889.63592</v>
       </c>
       <c r="P4" t="n">
-        <v>16010830220</v>
+        <v>10414244120</v>
       </c>
       <c r="Q4" t="n">
-        <v>321440945510</v>
+        <v>252710058410</v>
       </c>
       <c r="R4" t="n">
-        <v>19125865550</v>
+        <v>9727719980</v>
       </c>
       <c r="S4" t="n">
-        <v>15439566</v>
+        <v>15451401</v>
       </c>
       <c r="T4" t="n">
-        <v>15439566</v>
+        <v>15451401</v>
       </c>
       <c r="U4" t="n">
-        <v>1037</v>
+        <v>674</v>
       </c>
       <c r="V4" t="n">
-        <v>1037</v>
+        <v>674</v>
       </c>
       <c r="W4" t="n">
-        <v>16010830220</v>
+        <v>10414244120</v>
       </c>
       <c r="X4" t="n">
-        <v>16010830220</v>
+        <v>10414244120</v>
       </c>
       <c r="Y4" t="n">
-        <v>16010830220</v>
+        <v>10414244120</v>
       </c>
       <c r="Z4" t="n">
-        <v>16010830220</v>
+        <v>10414244120</v>
       </c>
       <c r="AA4" t="n">
-        <v>5302296690</v>
+        <v>2613257490</v>
       </c>
       <c r="AB4" t="n">
-        <v>21313126910</v>
+        <v>13027501610</v>
       </c>
       <c r="AC4" t="n">
-        <v>710780000</v>
+        <v>892141000</v>
       </c>
       <c r="AD4" t="n">
-        <v>123205000</v>
+        <v>-3793000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-123205000</v>
+        <v>3793000</v>
       </c>
       <c r="AF4" t="n">
-        <v>914796850</v>
+        <v>2453959690</v>
       </c>
       <c r="AG4" t="n">
-        <v>1150</v>
+        <v>1310</v>
       </c>
       <c r="AH4" t="n">
-        <v>1311000</v>
+        <v>100000</v>
       </c>
       <c r="AI4" t="n">
-        <v>916109000</v>
+        <v>2454061000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>19125865300</v>
+        <v>9727719600</v>
       </c>
       <c r="AK4" t="n">
-        <v>9813642000</v>
+        <v>8473800000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1069187000</v>
+        <v>34714000</v>
       </c>
       <c r="AM4" t="n">
-        <v>192935000</v>
+        <v>159390000</v>
       </c>
       <c r="AN4" t="n">
-        <v>517000</v>
+        <v>6200000</v>
       </c>
       <c r="AO4" t="n">
-        <v>192418000</v>
+        <v>153190000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3278887000</v>
+        <v>3166873000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2691919000</v>
+        <v>2620333000</v>
       </c>
       <c r="AR4" t="n">
-        <v>586968000</v>
+        <v>546540000</v>
       </c>
       <c r="AS4" t="n">
-        <v>28939507300</v>
+        <v>18201519600</v>
       </c>
       <c r="AT4" t="n">
-        <v>311627303510</v>
+        <v>244236258410</v>
       </c>
       <c r="AU4" t="n">
-        <v>340566810810</v>
+        <v>262437778010</v>
       </c>
       <c r="AV4" t="n">
-        <v>340566810810</v>
+        <v>262437778010</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-60123734.062886</v>
+        <v>42704379.177489</v>
       </c>
       <c r="C5" t="n">
-        <v>0.247524</v>
+        <v>0.200835</v>
       </c>
       <c r="D5" t="n">
-        <v>35973830020</v>
+        <v>4913742100</v>
       </c>
       <c r="E5" t="n">
-        <v>-242901000</v>
+        <v>212634000</v>
       </c>
       <c r="F5" t="n">
-        <v>-242901000</v>
+        <v>212634000</v>
       </c>
       <c r="G5" t="n">
-        <v>25395535400</v>
+        <v>5508284890</v>
       </c>
       <c r="H5" t="n">
-        <v>1979120000</v>
+        <v>1566517000</v>
       </c>
       <c r="I5" t="n">
-        <v>280493927190</v>
+        <v>211988698810</v>
       </c>
       <c r="J5" t="n">
-        <v>35730929020</v>
+        <v>5126376100</v>
       </c>
       <c r="K5" t="n">
-        <v>33751809020</v>
+        <v>3559859100</v>
       </c>
       <c r="L5" t="n">
-        <v>350771090</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2530000</v>
-      </c>
+        <v>2540333380</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>353301000</v>
+        <v>2540333000</v>
       </c>
       <c r="O5" t="n">
-        <v>25578312665.93711</v>
+        <v>5338355269.177489</v>
       </c>
       <c r="P5" t="n">
-        <v>25395535400</v>
+        <v>5508284890</v>
       </c>
       <c r="Q5" t="n">
-        <v>288998100190</v>
+        <v>220101647810</v>
       </c>
       <c r="R5" t="n">
-        <v>33148768680</v>
+        <v>3559859450</v>
       </c>
       <c r="S5" t="n">
-        <v>15447406</v>
+        <v>15429369</v>
       </c>
       <c r="T5" t="n">
-        <v>15447406</v>
+        <v>15429369</v>
       </c>
       <c r="U5" t="n">
-        <v>1644</v>
+        <v>357</v>
       </c>
       <c r="V5" t="n">
-        <v>1644</v>
+        <v>357</v>
       </c>
       <c r="W5" t="n">
-        <v>25395535400</v>
+        <v>5508284890</v>
       </c>
       <c r="X5" t="n">
-        <v>25395535400</v>
+        <v>5508284890</v>
       </c>
       <c r="Y5" t="n">
-        <v>25395535400</v>
+        <v>5508284890</v>
       </c>
       <c r="Z5" t="n">
-        <v>25395535400</v>
+        <v>5508284890</v>
       </c>
       <c r="AA5" t="n">
-        <v>8353743610</v>
+        <v>1384266530</v>
       </c>
       <c r="AB5" t="n">
-        <v>33749279020</v>
+        <v>6892551420</v>
       </c>
       <c r="AC5" t="n">
-        <v>220152000</v>
+        <v>593440000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-253416000</v>
+        <v>167374000</v>
       </c>
       <c r="AE5" t="n">
-        <v>253416000</v>
+        <v>-167374000</v>
       </c>
       <c r="AF5" t="n">
-        <v>350771090</v>
+        <v>2540333380</v>
       </c>
       <c r="AG5" t="n">
-        <v>-90</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>2530000</v>
-      </c>
+        <v>-380</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>353301000</v>
+        <v>2540333000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>33148768340</v>
+        <v>3559859100</v>
       </c>
       <c r="AK5" t="n">
-        <v>8504173000</v>
+        <v>8112949000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-311080000</v>
+        <v>-285435000</v>
       </c>
       <c r="AM5" t="n">
-        <v>207062000</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>144709000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>6200000</v>
+      </c>
       <c r="AO5" t="n">
-        <v>207062000</v>
+        <v>138509000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3076769000</v>
+        <v>3331577000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2420813000</v>
+        <v>2815619000</v>
       </c>
       <c r="AR5" t="n">
-        <v>655956000</v>
+        <v>515958000</v>
       </c>
       <c r="AS5" t="n">
-        <v>41652941340</v>
+        <v>11672808100</v>
       </c>
       <c r="AT5" t="n">
-        <v>280493927190</v>
+        <v>211988698810</v>
       </c>
       <c r="AU5" t="n">
-        <v>322146868530</v>
+        <v>223661506910</v>
       </c>
       <c r="AV5" t="n">
-        <v>322146868530</v>
+        <v>223661506910</v>
       </c>
     </row>
   </sheetData>
@@ -1571,7 +1571,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>260000</v>
@@ -1582,37 +1582,41 @@
       <c r="D2" t="n">
         <v>15702890</v>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>51215540</v>
+      </c>
       <c r="F2" t="n">
-        <v>194775471060</v>
+        <v>175493581770</v>
       </c>
       <c r="G2" t="n">
-        <v>195194764940</v>
+        <v>176070744520</v>
       </c>
       <c r="H2" t="n">
-        <v>158860150360</v>
+        <v>135043217400</v>
       </c>
       <c r="I2" t="n">
-        <v>194775471060</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>175493581770</v>
+      </c>
+      <c r="J2" t="n">
+        <v>51215540</v>
+      </c>
       <c r="K2" t="n">
-        <v>195194764940</v>
+        <v>176070744520</v>
       </c>
       <c r="L2" t="n">
-        <v>195194764940</v>
+        <v>176070744520</v>
       </c>
       <c r="M2" t="n">
-        <v>195194764600</v>
+        <v>176070744190</v>
       </c>
       <c r="N2" t="n">
-        <v>195194764940</v>
+        <v>176070744520</v>
       </c>
       <c r="O2" t="n">
         <v>849094000</v>
       </c>
       <c r="P2" t="n">
-        <v>184127036940</v>
+        <v>165003016520</v>
       </c>
       <c r="Q2" t="n">
         <v>3365377000</v>
@@ -1624,75 +1628,85 @@
         <v>8551445000</v>
       </c>
       <c r="T2" t="n">
-        <v>21674155920</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+        <v>36070032420</v>
+      </c>
+      <c r="U2" t="n">
+        <v>21380950</v>
+      </c>
+      <c r="V2" t="n">
+        <v>21380950</v>
+      </c>
+      <c r="W2" t="n">
+        <v>21380950</v>
+      </c>
       <c r="X2" t="n">
-        <v>21674155920</v>
+        <v>36048651460</v>
       </c>
       <c r="Y2" t="n">
-        <v>-230</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+        <v>700</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>29834590</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>29834590</v>
+      </c>
       <c r="AB2" t="n">
-        <v>20472816150</v>
+        <v>33129511760</v>
       </c>
       <c r="AC2" t="n">
-        <v>1751023320</v>
+        <v>2303401710</v>
       </c>
       <c r="AD2" t="n">
-        <v>951148150</v>
+        <v>7102430760</v>
       </c>
       <c r="AE2" t="n">
-        <v>17770644680</v>
+        <v>23723679290</v>
       </c>
       <c r="AF2" t="n">
-        <v>216868920520</v>
+        <v>212140776610</v>
       </c>
       <c r="AG2" t="n">
-        <v>36334614240</v>
+        <v>41048907750</v>
       </c>
       <c r="AH2" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="AI2" t="n">
-        <v>101932180</v>
+        <v>177936440</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1255553060</v>
+        <v>941104000</v>
       </c>
       <c r="AK2" t="n">
-        <v>3343789300</v>
+        <v>3996114090</v>
       </c>
       <c r="AL2" t="n">
-        <v>3200799300</v>
+        <v>3992614090</v>
       </c>
       <c r="AM2" t="n">
-        <v>142990000</v>
+        <v>3500000</v>
       </c>
       <c r="AN2" t="n">
-        <v>419293880</v>
+        <v>577162750</v>
       </c>
       <c r="AO2" t="n">
-        <v>419293880</v>
+        <v>577162750</v>
       </c>
       <c r="AP2" t="n">
-        <v>31214045810</v>
+        <v>35356590430</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-33159202000</v>
+        <v>-30015700000</v>
       </c>
       <c r="AR2" t="n">
-        <v>64373248000</v>
+        <v>65372290090</v>
       </c>
       <c r="AS2" t="n">
-        <v>3560653000</v>
+        <v>3608122090</v>
       </c>
       <c r="AT2" t="n">
-        <v>21852422000</v>
+        <v>22803995000</v>
       </c>
       <c r="AU2" t="n">
         <v>21853030000</v>
@@ -1704,54 +1718,54 @@
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>180534306280</v>
+        <v>171091868860</v>
       </c>
       <c r="AY2" t="n">
-        <v>-10</v>
+        <v>-170</v>
       </c>
       <c r="AZ2" t="n">
-        <v>389238000</v>
+        <v>243875000</v>
       </c>
       <c r="BA2" t="n">
-        <v>21481705320</v>
+        <v>41102160960</v>
       </c>
       <c r="BB2" t="n">
-        <v>-1684392000</v>
+        <v>-557585000</v>
       </c>
       <c r="BC2" t="n">
-        <v>320</v>
+        <v>-40</v>
       </c>
       <c r="BD2" t="n">
-        <v>11741813000</v>
+        <v>15787165000</v>
       </c>
       <c r="BE2" t="n">
-        <v>11424284000</v>
+        <v>25872581000</v>
       </c>
       <c r="BF2" t="n">
-        <v>288701000</v>
+        <v>59013000</v>
       </c>
       <c r="BG2" t="n">
-        <v>54120022000</v>
+        <v>77034929000</v>
       </c>
       <c r="BH2" t="n">
-        <v>-2574614000</v>
+        <v>-3023144000</v>
       </c>
       <c r="BI2" t="n">
-        <v>56694636000</v>
+        <v>80058073000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>104254639970</v>
+        <v>52651891070</v>
       </c>
       <c r="BK2" t="n">
-        <v>104254639970</v>
+        <v>52651891070</v>
       </c>
       <c r="BL2" t="n">
-        <v>104254640000</v>
+        <v>52651891000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>260000</v>
@@ -1762,37 +1776,41 @@
       <c r="D3" t="n">
         <v>15702890</v>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>13769220</v>
+      </c>
       <c r="F3" t="n">
-        <v>193929653590</v>
+        <v>188802941860</v>
       </c>
       <c r="G3" t="n">
-        <v>194512419670</v>
+        <v>189392647940</v>
       </c>
       <c r="H3" t="n">
-        <v>156320493730</v>
+        <v>150260245400</v>
       </c>
       <c r="I3" t="n">
-        <v>193929653590</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
+        <v>188802941860</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13769220</v>
+      </c>
       <c r="K3" t="n">
-        <v>194512419670</v>
+        <v>189392647940</v>
       </c>
       <c r="L3" t="n">
-        <v>194512419670</v>
+        <v>189392647940</v>
       </c>
       <c r="M3" t="n">
-        <v>194512419340</v>
+        <v>189392647610</v>
       </c>
       <c r="N3" t="n">
-        <v>194512419670</v>
+        <v>189392647940</v>
       </c>
       <c r="O3" t="n">
         <v>849094000</v>
       </c>
       <c r="P3" t="n">
-        <v>183444691670</v>
+        <v>178324919940</v>
       </c>
       <c r="Q3" t="n">
         <v>3365377000</v>
@@ -1804,75 +1822,79 @@
         <v>8551445000</v>
       </c>
       <c r="T3" t="n">
-        <v>26850104010</v>
+        <v>34897295820</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>26850104010</v>
+        <v>34897295820</v>
       </c>
       <c r="Y3" t="n">
-        <v>1030</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+        <v>370</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>13769220</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>13769220</v>
+      </c>
       <c r="AB3" t="n">
-        <v>25095301980</v>
+        <v>32228687450</v>
       </c>
       <c r="AC3" t="n">
-        <v>1168270760</v>
+        <v>1798447820</v>
       </c>
       <c r="AD3" t="n">
-        <v>1848579980</v>
+        <v>3721234450</v>
       </c>
       <c r="AE3" t="n">
-        <v>22078451240</v>
+        <v>26709005180</v>
       </c>
       <c r="AF3" t="n">
-        <v>221362523350</v>
+        <v>224289943430</v>
       </c>
       <c r="AG3" t="n">
-        <v>38191925610</v>
+        <v>39132402210</v>
       </c>
       <c r="AH3" t="n">
         <v>30</v>
       </c>
       <c r="AI3" t="n">
-        <v>110711370</v>
+        <v>452395360</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1531230900</v>
+        <v>1136266440</v>
       </c>
       <c r="AK3" t="n">
-        <v>3197591120</v>
+        <v>3382242130</v>
       </c>
       <c r="AL3" t="n">
-        <v>3098861120</v>
+        <v>3200542130</v>
       </c>
       <c r="AM3" t="n">
-        <v>98730000</v>
+        <v>181700000</v>
       </c>
       <c r="AN3" t="n">
-        <v>582766080</v>
+        <v>589706080</v>
       </c>
       <c r="AO3" t="n">
-        <v>582766080</v>
+        <v>589706080</v>
       </c>
       <c r="AP3" t="n">
-        <v>32769626110</v>
+        <v>33571792170</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-31618122000</v>
+        <v>-31725035000</v>
       </c>
       <c r="AR3" t="n">
-        <v>64387748000</v>
+        <v>65296827030</v>
       </c>
       <c r="AS3" t="n">
-        <v>3560653000</v>
+        <v>3573538030</v>
       </c>
       <c r="AT3" t="n">
-        <v>21866922000</v>
+        <v>22763116000</v>
       </c>
       <c r="AU3" t="n">
         <v>21853030000</v>
@@ -1884,54 +1906,54 @@
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>183170597740</v>
+        <v>185157541220</v>
       </c>
       <c r="AY3" t="n">
-        <v>-780</v>
+        <v>-100</v>
       </c>
       <c r="AZ3" t="n">
-        <v>207801000</v>
+        <v>325125000</v>
       </c>
       <c r="BA3" t="n">
-        <v>27333506180</v>
+        <v>26475158940</v>
       </c>
       <c r="BB3" t="n">
-        <v>-2109687000</v>
+        <v>-1497201000</v>
       </c>
       <c r="BC3" t="n">
-        <v>180</v>
+        <v>-60</v>
       </c>
       <c r="BD3" t="n">
-        <v>14543608000</v>
+        <v>12737465000</v>
       </c>
       <c r="BE3" t="n">
-        <v>14899585000</v>
+        <v>15234895000</v>
       </c>
       <c r="BF3" t="n">
-        <v>428946120</v>
+        <v>231809000</v>
       </c>
       <c r="BG3" t="n">
-        <v>55888731880</v>
+        <v>69316123000</v>
       </c>
       <c r="BH3" t="n">
-        <v>-3124386000</v>
+        <v>-3522789000</v>
       </c>
       <c r="BI3" t="n">
-        <v>55888731880</v>
+        <v>72838912000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>99311613340</v>
+        <v>88809325380</v>
       </c>
       <c r="BK3" t="n">
-        <v>99311613340</v>
+        <v>88809325380</v>
       </c>
       <c r="BL3" t="n">
-        <v>99311613000</v>
+        <v>88809325000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>260000</v>
@@ -1942,41 +1964,37 @@
       <c r="D4" t="n">
         <v>15702890</v>
       </c>
-      <c r="E4" t="n">
-        <v>13769220</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>188802941860</v>
+        <v>193929653590</v>
       </c>
       <c r="G4" t="n">
-        <v>189392647940</v>
+        <v>194512419670</v>
       </c>
       <c r="H4" t="n">
-        <v>150260245400</v>
+        <v>156320493730</v>
       </c>
       <c r="I4" t="n">
-        <v>188802941860</v>
-      </c>
-      <c r="J4" t="n">
-        <v>13769220</v>
-      </c>
+        <v>193929653590</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>189392647940</v>
+        <v>194512419670</v>
       </c>
       <c r="L4" t="n">
-        <v>189392647940</v>
+        <v>194512419670</v>
       </c>
       <c r="M4" t="n">
-        <v>189392647610</v>
+        <v>194512419340</v>
       </c>
       <c r="N4" t="n">
-        <v>189392647940</v>
+        <v>194512419670</v>
       </c>
       <c r="O4" t="n">
         <v>849094000</v>
       </c>
       <c r="P4" t="n">
-        <v>178324919940</v>
+        <v>183444691670</v>
       </c>
       <c r="Q4" t="n">
         <v>3365377000</v>
@@ -1988,79 +2006,75 @@
         <v>8551445000</v>
       </c>
       <c r="T4" t="n">
-        <v>34897295820</v>
+        <v>26850104010</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>34897295820</v>
+        <v>26850104010</v>
       </c>
       <c r="Y4" t="n">
-        <v>370</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>13769220</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>13769220</v>
-      </c>
+        <v>1030</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>32228687450</v>
+        <v>25095301980</v>
       </c>
       <c r="AC4" t="n">
-        <v>1798447820</v>
+        <v>1168270760</v>
       </c>
       <c r="AD4" t="n">
-        <v>3721234450</v>
+        <v>1848579980</v>
       </c>
       <c r="AE4" t="n">
-        <v>26709005180</v>
+        <v>22078451240</v>
       </c>
       <c r="AF4" t="n">
-        <v>224289943430</v>
+        <v>221362523350</v>
       </c>
       <c r="AG4" t="n">
-        <v>39132402210</v>
+        <v>38191925610</v>
       </c>
       <c r="AH4" t="n">
         <v>30</v>
       </c>
       <c r="AI4" t="n">
-        <v>452395360</v>
+        <v>110711370</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1136266440</v>
+        <v>1531230900</v>
       </c>
       <c r="AK4" t="n">
-        <v>3382242130</v>
+        <v>3197591120</v>
       </c>
       <c r="AL4" t="n">
-        <v>3200542130</v>
+        <v>3098861120</v>
       </c>
       <c r="AM4" t="n">
-        <v>181700000</v>
+        <v>98730000</v>
       </c>
       <c r="AN4" t="n">
-        <v>589706080</v>
+        <v>582766080</v>
       </c>
       <c r="AO4" t="n">
-        <v>589706080</v>
+        <v>582766080</v>
       </c>
       <c r="AP4" t="n">
-        <v>33571792170</v>
+        <v>32769626110</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-31725035000</v>
+        <v>-31618122000</v>
       </c>
       <c r="AR4" t="n">
-        <v>65296827030</v>
+        <v>64387748000</v>
       </c>
       <c r="AS4" t="n">
-        <v>3573538030</v>
+        <v>3560653000</v>
       </c>
       <c r="AT4" t="n">
-        <v>22763116000</v>
+        <v>21866922000</v>
       </c>
       <c r="AU4" t="n">
         <v>21853030000</v>
@@ -2072,54 +2086,54 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>185157541220</v>
+        <v>183170597740</v>
       </c>
       <c r="AY4" t="n">
-        <v>-100</v>
+        <v>-780</v>
       </c>
       <c r="AZ4" t="n">
-        <v>325125000</v>
+        <v>207801000</v>
       </c>
       <c r="BA4" t="n">
-        <v>26475158940</v>
+        <v>27333506180</v>
       </c>
       <c r="BB4" t="n">
-        <v>-1497201000</v>
+        <v>-2109687000</v>
       </c>
       <c r="BC4" t="n">
-        <v>-60</v>
+        <v>180</v>
       </c>
       <c r="BD4" t="n">
-        <v>12737465000</v>
+        <v>14543608000</v>
       </c>
       <c r="BE4" t="n">
-        <v>15234895000</v>
+        <v>14899585000</v>
       </c>
       <c r="BF4" t="n">
-        <v>231809000</v>
+        <v>428946120</v>
       </c>
       <c r="BG4" t="n">
-        <v>69316123000</v>
+        <v>55888731880</v>
       </c>
       <c r="BH4" t="n">
-        <v>-3522789000</v>
+        <v>-3124386000</v>
       </c>
       <c r="BI4" t="n">
-        <v>72838912000</v>
+        <v>55888731880</v>
       </c>
       <c r="BJ4" t="n">
-        <v>88809325380</v>
+        <v>99311613340</v>
       </c>
       <c r="BK4" t="n">
-        <v>88809325380</v>
+        <v>99311613340</v>
       </c>
       <c r="BL4" t="n">
-        <v>88809325000</v>
+        <v>99311613000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>260000</v>
@@ -2130,41 +2144,37 @@
       <c r="D5" t="n">
         <v>15702890</v>
       </c>
-      <c r="E5" t="n">
-        <v>51215540</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>175493581770</v>
+        <v>194775471060</v>
       </c>
       <c r="G5" t="n">
-        <v>176070744520</v>
+        <v>195194764940</v>
       </c>
       <c r="H5" t="n">
-        <v>135043217400</v>
+        <v>158860150360</v>
       </c>
       <c r="I5" t="n">
-        <v>175493581770</v>
-      </c>
-      <c r="J5" t="n">
-        <v>51215540</v>
-      </c>
+        <v>194775471060</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>176070744520</v>
+        <v>195194764940</v>
       </c>
       <c r="L5" t="n">
-        <v>176070744520</v>
+        <v>195194764940</v>
       </c>
       <c r="M5" t="n">
-        <v>176070744190</v>
+        <v>195194764600</v>
       </c>
       <c r="N5" t="n">
-        <v>176070744520</v>
+        <v>195194764940</v>
       </c>
       <c r="O5" t="n">
         <v>849094000</v>
       </c>
       <c r="P5" t="n">
-        <v>165003016520</v>
+        <v>184127036940</v>
       </c>
       <c r="Q5" t="n">
         <v>3365377000</v>
@@ -2176,85 +2186,75 @@
         <v>8551445000</v>
       </c>
       <c r="T5" t="n">
-        <v>36070032420</v>
-      </c>
-      <c r="U5" t="n">
-        <v>21380950</v>
-      </c>
-      <c r="V5" t="n">
-        <v>21380950</v>
-      </c>
-      <c r="W5" t="n">
-        <v>21380950</v>
-      </c>
+        <v>21674155920</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>36048651460</v>
+        <v>21674155920</v>
       </c>
       <c r="Y5" t="n">
-        <v>700</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>29834590</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>29834590</v>
-      </c>
+        <v>-230</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>33129511760</v>
+        <v>20472816150</v>
       </c>
       <c r="AC5" t="n">
-        <v>2303401710</v>
+        <v>1751023320</v>
       </c>
       <c r="AD5" t="n">
-        <v>7102430760</v>
+        <v>951148150</v>
       </c>
       <c r="AE5" t="n">
-        <v>23723679290</v>
+        <v>17770644680</v>
       </c>
       <c r="AF5" t="n">
-        <v>212140776610</v>
+        <v>216868920520</v>
       </c>
       <c r="AG5" t="n">
-        <v>41048907750</v>
+        <v>36334614240</v>
       </c>
       <c r="AH5" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AI5" t="n">
-        <v>177936440</v>
+        <v>101932180</v>
       </c>
       <c r="AJ5" t="n">
-        <v>941104000</v>
+        <v>1255553060</v>
       </c>
       <c r="AK5" t="n">
-        <v>3996114090</v>
+        <v>3343789300</v>
       </c>
       <c r="AL5" t="n">
-        <v>3992614090</v>
+        <v>3200799300</v>
       </c>
       <c r="AM5" t="n">
-        <v>3500000</v>
+        <v>142990000</v>
       </c>
       <c r="AN5" t="n">
-        <v>577162750</v>
+        <v>419293880</v>
       </c>
       <c r="AO5" t="n">
-        <v>577162750</v>
+        <v>419293880</v>
       </c>
       <c r="AP5" t="n">
-        <v>35356590430</v>
+        <v>31214045810</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-30015700000</v>
+        <v>-33159202000</v>
       </c>
       <c r="AR5" t="n">
-        <v>65372290090</v>
+        <v>64373248000</v>
       </c>
       <c r="AS5" t="n">
-        <v>3608122090</v>
+        <v>3560653000</v>
       </c>
       <c r="AT5" t="n">
-        <v>22803995000</v>
+        <v>21852422000</v>
       </c>
       <c r="AU5" t="n">
         <v>21853030000</v>
@@ -2266,49 +2266,49 @@
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>171091868860</v>
+        <v>180534306280</v>
       </c>
       <c r="AY5" t="n">
-        <v>-170</v>
+        <v>-10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>243875000</v>
+        <v>389238000</v>
       </c>
       <c r="BA5" t="n">
-        <v>41102160960</v>
+        <v>21481705320</v>
       </c>
       <c r="BB5" t="n">
-        <v>-557585000</v>
+        <v>-1684392000</v>
       </c>
       <c r="BC5" t="n">
-        <v>-40</v>
+        <v>320</v>
       </c>
       <c r="BD5" t="n">
-        <v>15787165000</v>
+        <v>11741813000</v>
       </c>
       <c r="BE5" t="n">
-        <v>25872581000</v>
+        <v>11424284000</v>
       </c>
       <c r="BF5" t="n">
-        <v>59013000</v>
+        <v>288701000</v>
       </c>
       <c r="BG5" t="n">
-        <v>77034929000</v>
+        <v>54120022000</v>
       </c>
       <c r="BH5" t="n">
-        <v>-3023144000</v>
+        <v>-2574614000</v>
       </c>
       <c r="BI5" t="n">
-        <v>80058073000</v>
+        <v>56694636000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>52651891070</v>
+        <v>104254639970</v>
       </c>
       <c r="BK5" t="n">
-        <v>52651891070</v>
+        <v>104254639970</v>
       </c>
       <c r="BL5" t="n">
-        <v>52651891000</v>
+        <v>104254640000</v>
       </c>
     </row>
   </sheetData>
@@ -2544,508 +2544,508 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>9244984540</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>-7093947400</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1131192890</v>
+      </c>
       <c r="D2" t="n">
-        <v>104254639970</v>
+        <v>52651891070</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>99311613340</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>61467951640</v>
+      </c>
+      <c r="G2" t="n">
+        <v>16384770</v>
+      </c>
       <c r="H2" t="n">
-        <v>4943026630</v>
+        <v>-8832445340</v>
       </c>
       <c r="I2" t="n">
-        <v>-4632867000</v>
+        <v>-3901599940</v>
       </c>
       <c r="J2" t="n">
-        <v>-4632867000</v>
+        <v>-3860722500</v>
       </c>
       <c r="K2" t="n">
-        <v>330909090</v>
+        <v>1031909110</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>1000000</v>
+        <v>2000000000</v>
       </c>
       <c r="N2" t="n">
-        <v>61071297320</v>
+        <v>13153041000</v>
       </c>
       <c r="O2" t="n">
-        <v>-61070297320</v>
+        <v>-11153041000</v>
       </c>
       <c r="P2" t="n">
-        <v>329909090</v>
+        <v>70300000</v>
       </c>
       <c r="Q2" t="n">
-        <v>329909090</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+        <v>90000000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-19700000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-1038390890</v>
+      </c>
+      <c r="T2" t="n">
+        <v>73102000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-1111492890</v>
+      </c>
       <c r="V2" t="n">
-        <v>9244984540</v>
+        <v>-5962754510</v>
       </c>
       <c r="W2" t="n">
-        <v>-1955006390</v>
+        <v>-2574003310</v>
       </c>
       <c r="X2" t="n">
-        <v>2471482550</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>256578140</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-2529910</v>
+      </c>
       <c r="Z2" t="n">
-        <v>3317486000</v>
+        <v>-38740140000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-500000000</v>
+        <v>-420000000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-87181000</v>
+        <v>312968000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-466281000</v>
+        <v>881594000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-3725055000</v>
+        <v>-565000000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-181437000</v>
+        <v>-7016000</v>
       </c>
       <c r="AF2" t="n">
-        <v>5851801000</v>
+        <v>-17523335000</v>
       </c>
       <c r="AG2" t="n">
-        <v>2425639000</v>
+        <v>-21419351000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-2540333000</v>
+        <v>-350771000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-549772000</v>
+        <v>-562378000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1384267000</v>
+        <v>8353743000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1566517000</v>
+        <v>1979120000</v>
       </c>
       <c r="AL2" t="n">
-        <v>10940000</v>
+        <v>657000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1555577000</v>
+        <v>1978463000</v>
       </c>
       <c r="AN2" t="n">
-        <v>264692000</v>
+        <v>255576000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-45260000</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>-10515000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-16385000</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>-177374000</v>
+        <v>53416000</v>
       </c>
       <c r="AR2" t="n">
-        <v>5508285000</v>
+        <v>25395535000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>14979077160</v>
+        <v>38592427490</v>
       </c>
       <c r="C3" t="n">
-        <v>-967214170</v>
+        <v>-172232240</v>
       </c>
       <c r="D3" t="n">
-        <v>99311613340</v>
+        <v>88809325380</v>
       </c>
       <c r="E3" t="n">
         <v>-10</v>
       </c>
       <c r="F3" t="n">
-        <v>88809325380</v>
+        <v>52651891070</v>
       </c>
       <c r="G3" t="n">
-        <v>-20408350</v>
+        <v>-35991410</v>
       </c>
       <c r="H3" t="n">
-        <v>10522696320</v>
+        <v>36193425730</v>
       </c>
       <c r="I3" t="n">
-        <v>-4636961460</v>
+        <v>-3117242550</v>
       </c>
       <c r="J3" t="n">
-        <v>-4632867000</v>
+        <v>-3088578000</v>
       </c>
       <c r="K3" t="n">
-        <v>-786633550</v>
+        <v>546008550</v>
       </c>
       <c r="L3" t="n">
-        <v>24000000</v>
+        <v>10000000</v>
       </c>
       <c r="M3" t="n">
-        <v>149367820</v>
+        <v>691513520</v>
       </c>
       <c r="N3" t="n">
-        <v>57154638450</v>
+        <v>869713520</v>
       </c>
       <c r="O3" t="n">
-        <v>-57005270630</v>
+        <v>-178200000</v>
       </c>
       <c r="P3" t="n">
-        <v>-4000000</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>-17000000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>14000000</v>
+      </c>
       <c r="R3" t="n">
-        <v>-4000000</v>
+        <v>-31000000</v>
       </c>
       <c r="S3" t="n">
-        <v>-956001370</v>
+        <v>-138504970</v>
       </c>
       <c r="T3" t="n">
-        <v>7212800</v>
+        <v>2727270</v>
       </c>
       <c r="U3" t="n">
-        <v>-963214170</v>
+        <v>-141232240</v>
       </c>
       <c r="V3" t="n">
-        <v>15946291330</v>
+        <v>38764659730</v>
       </c>
       <c r="W3" t="n">
-        <v>-4730975370</v>
+        <v>-8984252280</v>
       </c>
       <c r="X3" t="n">
-        <v>2322369400</v>
+        <v>641458180</v>
       </c>
       <c r="Y3" t="n">
-        <v>-99530</v>
+        <v>-1311440</v>
       </c>
       <c r="Z3" t="n">
-        <v>6020786000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-618029000</v>
-      </c>
+        <v>23895906000</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>-188861000</v>
+        <v>20094000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-709323000</v>
+        <v>-124078000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-5260731000</v>
+        <v>2480373000</v>
       </c>
       <c r="AE3" t="n">
-        <v>117324000</v>
+        <v>-81249000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-858347000</v>
+        <v>14627002000</v>
       </c>
       <c r="AG3" t="n">
-        <v>13538753000</v>
+        <v>6973764000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-2455230000</v>
+        <v>-1046633000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-267921000</v>
+        <v>759504000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2613257000</v>
+        <v>5302297000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1766057000</v>
+        <v>1922804000</v>
       </c>
       <c r="AL3" t="n">
-        <v>10940000</v>
+        <v>4457000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1755117000</v>
+        <v>1918347000</v>
       </c>
       <c r="AN3" t="n">
-        <v>148206000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>102397000</v>
-      </c>
+        <v>230789000</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>20408000</v>
+        <v>35991000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-7207000</v>
+        <v>-2723000</v>
       </c>
       <c r="AR3" t="n">
-        <v>10414244000</v>
+        <v>16010830000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>38592427490</v>
+        <v>14979077160</v>
       </c>
       <c r="C4" t="n">
-        <v>-172232240</v>
+        <v>-967214170</v>
       </c>
       <c r="D4" t="n">
-        <v>88809325380</v>
+        <v>99311613340</v>
       </c>
       <c r="E4" t="n">
         <v>-10</v>
       </c>
       <c r="F4" t="n">
-        <v>52651891070</v>
+        <v>88809325380</v>
       </c>
       <c r="G4" t="n">
-        <v>-35991410</v>
+        <v>-20408350</v>
       </c>
       <c r="H4" t="n">
-        <v>36193425730</v>
+        <v>10522696320</v>
       </c>
       <c r="I4" t="n">
-        <v>-3117242550</v>
+        <v>-4636961460</v>
       </c>
       <c r="J4" t="n">
-        <v>-3088578000</v>
+        <v>-4632867000</v>
       </c>
       <c r="K4" t="n">
-        <v>546008550</v>
+        <v>-786633550</v>
       </c>
       <c r="L4" t="n">
-        <v>10000000</v>
+        <v>24000000</v>
       </c>
       <c r="M4" t="n">
-        <v>691513520</v>
+        <v>149367820</v>
       </c>
       <c r="N4" t="n">
-        <v>869713520</v>
+        <v>57154638450</v>
       </c>
       <c r="O4" t="n">
-        <v>-178200000</v>
+        <v>-57005270630</v>
       </c>
       <c r="P4" t="n">
-        <v>-17000000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>14000000</v>
-      </c>
+        <v>-4000000</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>-31000000</v>
+        <v>-4000000</v>
       </c>
       <c r="S4" t="n">
-        <v>-138504970</v>
+        <v>-956001370</v>
       </c>
       <c r="T4" t="n">
-        <v>2727270</v>
+        <v>7212800</v>
       </c>
       <c r="U4" t="n">
-        <v>-141232240</v>
+        <v>-963214170</v>
       </c>
       <c r="V4" t="n">
-        <v>38764659730</v>
+        <v>15946291330</v>
       </c>
       <c r="W4" t="n">
-        <v>-8984252280</v>
+        <v>-4730975370</v>
       </c>
       <c r="X4" t="n">
-        <v>641458180</v>
+        <v>2322369400</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1311440</v>
+        <v>-99530</v>
       </c>
       <c r="Z4" t="n">
-        <v>23895906000</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
+        <v>6020786000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-618029000</v>
+      </c>
       <c r="AB4" t="n">
-        <v>20094000</v>
+        <v>-188861000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-124078000</v>
+        <v>-709323000</v>
       </c>
       <c r="AD4" t="n">
-        <v>2480373000</v>
+        <v>-5260731000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-81249000</v>
+        <v>117324000</v>
       </c>
       <c r="AF4" t="n">
-        <v>14627002000</v>
+        <v>-858347000</v>
       </c>
       <c r="AG4" t="n">
-        <v>6973764000</v>
+        <v>13538753000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1046633000</v>
+        <v>-2455230000</v>
       </c>
       <c r="AI4" t="n">
-        <v>759504000</v>
+        <v>-267921000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5302297000</v>
+        <v>2613257000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1922804000</v>
+        <v>1766057000</v>
       </c>
       <c r="AL4" t="n">
-        <v>4457000</v>
+        <v>10940000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1918347000</v>
+        <v>1755117000</v>
       </c>
       <c r="AN4" t="n">
-        <v>230789000</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
+        <v>148206000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>102397000</v>
+      </c>
       <c r="AP4" t="n">
-        <v>35991000</v>
+        <v>20408000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-2723000</v>
+        <v>-7207000</v>
       </c>
       <c r="AR4" t="n">
-        <v>16010830000</v>
+        <v>10414244000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-7093947400</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-1131192890</v>
-      </c>
+        <v>9244984540</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>52651891070</v>
+        <v>104254639970</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>61467951640</v>
-      </c>
-      <c r="G5" t="n">
-        <v>16384770</v>
-      </c>
+        <v>99311613340</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-8832445340</v>
+        <v>4943026630</v>
       </c>
       <c r="I5" t="n">
-        <v>-3901599940</v>
+        <v>-4632867000</v>
       </c>
       <c r="J5" t="n">
-        <v>-3860722500</v>
+        <v>-4632867000</v>
       </c>
       <c r="K5" t="n">
-        <v>1031909110</v>
+        <v>330909090</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>2000000000</v>
+        <v>1000000</v>
       </c>
       <c r="N5" t="n">
-        <v>13153041000</v>
+        <v>61071297320</v>
       </c>
       <c r="O5" t="n">
-        <v>-11153041000</v>
+        <v>-61070297320</v>
       </c>
       <c r="P5" t="n">
-        <v>70300000</v>
+        <v>329909090</v>
       </c>
       <c r="Q5" t="n">
-        <v>90000000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-19700000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-1038390890</v>
-      </c>
-      <c r="T5" t="n">
-        <v>73102000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-1111492890</v>
-      </c>
+        <v>329909090</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-5962754510</v>
+        <v>9244984540</v>
       </c>
       <c r="W5" t="n">
-        <v>-2574003310</v>
+        <v>-1955006390</v>
       </c>
       <c r="X5" t="n">
-        <v>256578140</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-2529910</v>
-      </c>
+        <v>2471482550</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>-38740140000</v>
+        <v>3317486000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-420000000</v>
+        <v>-500000000</v>
       </c>
       <c r="AB5" t="n">
-        <v>312968000</v>
+        <v>-87181000</v>
       </c>
       <c r="AC5" t="n">
-        <v>881594000</v>
+        <v>-466281000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-565000000</v>
+        <v>-3725055000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-7016000</v>
+        <v>-181437000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-17523335000</v>
+        <v>5851801000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-21419351000</v>
+        <v>2425639000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-350771000</v>
+        <v>-2540333000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-562378000</v>
+        <v>-549772000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8353743000</v>
+        <v>1384267000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1979120000</v>
+        <v>1566517000</v>
       </c>
       <c r="AL5" t="n">
-        <v>657000</v>
+        <v>10940000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1978463000</v>
+        <v>1555577000</v>
       </c>
       <c r="AN5" t="n">
-        <v>255576000</v>
+        <v>264692000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-10515000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-16385000</v>
-      </c>
+        <v>-45260000</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>53416000</v>
+        <v>-177374000</v>
       </c>
       <c r="AR5" t="n">
-        <v>25395535000</v>
+        <v>5508285000</v>
       </c>
     </row>
   </sheetData>
@@ -3059,7 +3059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EC2"/>
+  <dimension ref="A1:ED2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3505,225 +3505,230 @@
       </c>
       <c r="CK1" t="inlineStr">
         <is>
+          <t>earningsGrowth</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3817,34 +3822,34 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>4830</v>
+        <v>4695</v>
       </c>
       <c r="T2" t="n">
-        <v>4820</v>
+        <v>4695</v>
       </c>
       <c r="U2" t="n">
-        <v>4715</v>
+        <v>4645</v>
       </c>
       <c r="V2" t="n">
-        <v>4850</v>
+        <v>4700</v>
       </c>
       <c r="W2" t="n">
-        <v>4830</v>
+        <v>4695</v>
       </c>
       <c r="X2" t="n">
-        <v>4820</v>
+        <v>4695</v>
       </c>
       <c r="Y2" t="n">
-        <v>4715</v>
+        <v>4645</v>
       </c>
       <c r="Z2" t="n">
-        <v>4850</v>
+        <v>4700</v>
       </c>
       <c r="AA2" t="n">
         <v>300</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.21</v>
+        <v>6.39</v>
       </c>
       <c r="AC2" t="n">
         <v>1766966400</v>
@@ -3856,28 +3861,28 @@
         <v>5.67</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.328</v>
+        <v>0.308</v>
       </c>
       <c r="AG2" t="n">
-        <v>42696</v>
+        <v>4226</v>
       </c>
       <c r="AH2" t="n">
-        <v>42696</v>
+        <v>4226</v>
       </c>
       <c r="AI2" t="n">
-        <v>102147</v>
+        <v>115182</v>
       </c>
       <c r="AJ2" t="n">
-        <v>71251</v>
+        <v>92606</v>
       </c>
       <c r="AK2" t="n">
-        <v>71251</v>
+        <v>92606</v>
       </c>
       <c r="AL2" t="n">
-        <v>4750</v>
+        <v>4640</v>
       </c>
       <c r="AM2" t="n">
-        <v>4845</v>
+        <v>4645</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -3886,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>74666377216</v>
+        <v>71732224000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>74589158700</v>
+        <v>74203086450</v>
       </c>
       <c r="AR2" t="n">
         <v>4110</v>
@@ -3904,13 +3909,13 @@
         <v>525</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.3347883</v>
+        <v>0.32163218</v>
       </c>
       <c r="AW2" t="n">
-        <v>4786.3</v>
+        <v>4892.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>4607.75</v>
+        <v>4633.975</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
@@ -3921,7 +3926,7 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-37398491136</v>
+        <v>-39560495104</v>
       </c>
       <c r="BB2" t="n">
         <v>0.03352</v>
@@ -3933,7 +3938,7 @@
         <v>15442890</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.58522</v>
+        <v>0.5950800000000001</v>
       </c>
       <c r="BF2" t="n">
         <v>0</v>
@@ -3965,16 +3970,16 @@
         <v>1072656000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.168</v>
+        <v>-0.177</v>
       </c>
       <c r="BP2" t="n">
-        <v>-4.678</v>
+        <v>-4.948</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.039827824</v>
+        <v>0.04570186</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BS2" t="n">
         <v>300</v>
@@ -3988,7 +3993,7 @@
         </is>
       </c>
       <c r="BV2" t="n">
-        <v>4835</v>
+        <v>4645</v>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
@@ -4017,7 +4022,7 @@
         <v>223025643520</v>
       </c>
       <c r="CE2" t="n">
-        <v>14114.083</v>
+        <v>14441.963</v>
       </c>
       <c r="CF2" t="n">
         <v>0.01895</v>
@@ -4035,174 +4040,177 @@
         <v>10435102720</v>
       </c>
       <c r="CK2" t="n">
+        <v>1.568</v>
+      </c>
+      <c r="CL2" t="n">
         <v>0.097</v>
       </c>
-      <c r="CL2" t="n">
+      <c r="CM2" t="n">
         <v>0.06597</v>
       </c>
-      <c r="CM2" t="n">
+      <c r="CN2" t="n">
         <v>0.03585</v>
       </c>
-      <c r="CN2" t="n">
+      <c r="CO2" t="n">
         <v>0.02691</v>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>017480.KQ</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="CU2" t="b">
+      <c r="CV2" t="b">
         <v>0</v>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CX2" t="n">
+        <v>-1.0649627</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>4645</v>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>SAMSCO</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>-50</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>4645.0 - 4700.0</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>115182</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>535</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0.13017032</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>4110.0 - 6140.0</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>-1495</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.24348535</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>4.570186</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-247.7002</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.050626483</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>11.024902</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.0023791457</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>20</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>20</v>
+      </c>
+      <c r="DR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>979084800000</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DV2" t="n">
+        <v>1782174813</v>
+      </c>
+      <c r="DW2" t="inlineStr">
         <is>
           <t>KOE</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>Asia/Seoul</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>KST</t>
         </is>
       </c>
-      <c r="DA2" t="n">
+      <c r="DZ2" t="n">
         <v>32400000</v>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>kr_market</t>
         </is>
       </c>
-      <c r="DC2" t="b">
+      <c r="EB2" t="b">
         <v>0</v>
       </c>
-      <c r="DD2" t="n">
-        <v>48.700195</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>0.010174915</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>227.25</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>0.04931908</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>20</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>20</v>
-      </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>1780381830</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>SAMSCO</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>Samhyun Steel Co., Ltd.</t>
         </is>
       </c>
-      <c r="DO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>979084800000</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>4715.0 - 4850.0</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>102147</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>725</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0.17639902</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>4110.0 - 6140.0</t>
-        </is>
-      </c>
-      <c r="DX2" t="n">
-        <v>-1305</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.21254072</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>3.9827824</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.10351967</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>4835</v>
-      </c>
-      <c r="EC2" t="inlineStr"/>
+      <c r="ED2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
